--- a/Sample_project_type.xlsx
+++ b/Sample_project_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yeroslaviz/ownCloud/ownCloud_projects/Core_facilities/Proteomics_Corefacility_BarbaraS/mscf-vm/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yeroslaviz/Documents/GitHub/BCFMS-project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9720FB-EC1D-4BBA-B891-3D4A3ACE713D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2290AA19-6669-4441-AA59-3EF9DA6F2DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17540" yWindow="5260" windowWidth="22680" windowHeight="20320" xr2:uid="{EA36B8D9-F511-4F01-881F-EA08A4F151C1}"/>
+    <workbookView xWindow="20140" yWindow="2700" windowWidth="43020" windowHeight="31440" xr2:uid="{EA36B8D9-F511-4F01-881F-EA08A4F151C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>proteomics project type</t>
   </si>
@@ -44,15 +44,9 @@
     <t>Protein ID</t>
   </si>
   <si>
-    <t>Protein coverage /PTM</t>
-  </si>
-  <si>
     <t>Interaction Proteomics</t>
   </si>
   <si>
-    <t>Total proteome</t>
-  </si>
-  <si>
     <t>PTMomics (global, enrichment)</t>
   </si>
   <si>
@@ -62,21 +56,9 @@
     <t>proteomics sample type</t>
   </si>
   <si>
-    <t>in-solution digest</t>
-  </si>
-  <si>
-    <t>Gel band /gel lane</t>
-  </si>
-  <si>
     <t xml:space="preserve">On-beads </t>
   </si>
   <si>
-    <t>Cell pellet</t>
-  </si>
-  <si>
-    <t>Protein pellet</t>
-  </si>
-  <si>
     <t>Supernatent</t>
   </si>
   <si>
@@ -98,15 +80,6 @@
     <t>metabolomics sample type</t>
   </si>
   <si>
-    <t>cell pellet</t>
-  </si>
-  <si>
-    <t>supernatent</t>
-  </si>
-  <si>
-    <t>protein pellet</t>
-  </si>
-  <si>
     <t>metabolomics analysis type</t>
   </si>
   <si>
@@ -128,27 +101,12 @@
     <t>intact project type</t>
   </si>
   <si>
-    <t>Native protein complex</t>
-  </si>
-  <si>
     <t>Protein (QC)</t>
   </si>
   <si>
     <t>Protein (high resolution)</t>
   </si>
   <si>
-    <t>Small molecule (QC)</t>
-  </si>
-  <si>
-    <t>in-solution</t>
-  </si>
-  <si>
-    <t>powder</t>
-  </si>
-  <si>
-    <t>in-solution, Flow injection</t>
-  </si>
-  <si>
     <t>Metabolomics</t>
   </si>
   <si>
@@ -159,6 +117,39 @@
   </si>
   <si>
     <t>both</t>
+  </si>
+  <si>
+    <t>Cell Pellet</t>
+  </si>
+  <si>
+    <t>Protein Pellet</t>
+  </si>
+  <si>
+    <t>Total Proteome</t>
+  </si>
+  <si>
+    <t>Protein Coverage / PTM</t>
+  </si>
+  <si>
+    <t>In-solution Digest</t>
+  </si>
+  <si>
+    <t>Gel Band /Gel Lane</t>
+  </si>
+  <si>
+    <t>Small Molecule (QC)</t>
+  </si>
+  <si>
+    <t>Native Protein Complex</t>
+  </si>
+  <si>
+    <t>In-solution, Flow injection</t>
+  </si>
+  <si>
+    <t>In-solution</t>
+  </si>
+  <si>
+    <t>Powder</t>
   </si>
 </sst>
 </file>
@@ -571,19 +562,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -594,13 +585,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -608,13 +599,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -628,13 +619,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -642,16 +633,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>40</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -659,16 +650,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -676,16 +667,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H7">
         <v>18</v>
@@ -693,44 +684,44 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -738,19 +729,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -758,19 +749,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -778,7 +769,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -794,7 +785,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -802,7 +793,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -810,7 +801,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -818,7 +809,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -826,7 +817,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>70</v>
